--- a/input/scenario_CPI.xlsx
+++ b/input/scenario_CPI.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\labsim\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76499A2B-748F-401E-866D-FF42A386CCE6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5F19AB-4865-7A49-B28C-52548C7BD211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="390" windowWidth="38370" windowHeight="20370" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="600" windowWidth="38380" windowHeight="19700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
     <sheet name="UK" sheetId="2" r:id="rId2"/>
-    <sheet name="IT" sheetId="4" r:id="rId3"/>
-    <sheet name="UK_series-080321" sheetId="3" r:id="rId4"/>
+    <sheet name="UK_series-080321" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,14 +27,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="545">
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>This file contains CPI values by year by country. These are used to deflate the monetary values in the donor population to the starting year of the simulation.</t>
-  </si>
-  <si>
     <t>Year</t>
   </si>
   <si>
@@ -1663,6 +1659,9 @@
   </si>
   <si>
     <t>2021 JAN</t>
+  </si>
+  <si>
+    <t>This file contains CPI values by year. These are used to deflate the monetary values in the donor population to the starting year of the simulation.</t>
   </si>
 </sst>
 </file>
@@ -1983,12 +1982,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1996,9 +1995,9 @@
         <v>44263</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>544</v>
       </c>
     </row>
   </sheetData>
@@ -2009,17 +2008,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5368A556-88DB-4602-9465-944BD364475C}">
   <dimension ref="A1:B74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1988</v>
       </c>
@@ -2027,7 +2026,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1989</v>
       </c>
@@ -2035,7 +2034,7 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1990</v>
       </c>
@@ -2043,7 +2042,7 @@
         <v>55.9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1991</v>
       </c>
@@ -2051,7 +2050,7 @@
         <v>60.1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1992</v>
       </c>
@@ -2059,7 +2058,7 @@
         <v>62.6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1993</v>
       </c>
@@ -2067,7 +2066,7 @@
         <v>64.2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1994</v>
       </c>
@@ -2075,7 +2074,7 @@
         <v>65.5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1995</v>
       </c>
@@ -2083,7 +2082,7 @@
         <v>67.2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1996</v>
       </c>
@@ -2091,7 +2090,7 @@
         <v>68.8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1997</v>
       </c>
@@ -2099,7 +2098,7 @@
         <v>70.099999999999994</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1998</v>
       </c>
@@ -2107,7 +2106,7 @@
         <v>71.2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1999</v>
       </c>
@@ -2115,7 +2114,7 @@
         <v>72.099999999999994</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2000</v>
       </c>
@@ -2123,7 +2122,7 @@
         <v>72.7</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2001</v>
       </c>
@@ -2131,7 +2130,7 @@
         <v>73.599999999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>2002</v>
       </c>
@@ -2139,7 +2138,7 @@
         <v>74.5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2003</v>
       </c>
@@ -2147,7 +2146,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2004</v>
       </c>
@@ -2155,7 +2154,7 @@
         <v>76.5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>2005</v>
       </c>
@@ -2163,7 +2162,7 @@
         <v>78.099999999999994</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>2006</v>
       </c>
@@ -2171,7 +2170,7 @@
         <v>79.900000000000006</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>2007</v>
       </c>
@@ -2179,7 +2178,7 @@
         <v>81.8</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>2008</v>
       </c>
@@ -2187,7 +2186,7 @@
         <v>84.7</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>2009</v>
       </c>
@@ -2195,7 +2194,7 @@
         <v>86.6</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>2010</v>
       </c>
@@ -2203,7 +2202,7 @@
         <v>89.4</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>2011</v>
       </c>
@@ -2211,7 +2210,7 @@
         <v>93.4</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>2012</v>
       </c>
@@ -2219,7 +2218,7 @@
         <v>96.1</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>2013</v>
       </c>
@@ -2227,7 +2226,7 @@
         <v>98.5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>2014</v>
       </c>
@@ -2235,7 +2234,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>2015</v>
       </c>
@@ -2243,7 +2242,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>2016</v>
       </c>
@@ -2251,7 +2250,7 @@
         <v>100.7</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>2017</v>
       </c>
@@ -2259,7 +2258,7 @@
         <v>103.4</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>2018</v>
       </c>
@@ -2267,7 +2266,7 @@
         <v>105.9</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>2019</v>
       </c>
@@ -2275,7 +2274,7 @@
         <v>107.8</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>2020</v>
       </c>
@@ -2283,7 +2282,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>2021</v>
       </c>
@@ -2291,7 +2290,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>2022</v>
       </c>
@@ -2299,7 +2298,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>2023</v>
       </c>
@@ -2307,7 +2306,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>2024</v>
       </c>
@@ -2315,7 +2314,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>2025</v>
       </c>
@@ -2323,7 +2322,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>2026</v>
       </c>
@@ -2331,7 +2330,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>2027</v>
       </c>
@@ -2339,7 +2338,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>2028</v>
       </c>
@@ -2347,7 +2346,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>2029</v>
       </c>
@@ -2355,7 +2354,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>2030</v>
       </c>
@@ -2363,7 +2362,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>2031</v>
       </c>
@@ -2371,7 +2370,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>2032</v>
       </c>
@@ -2379,7 +2378,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>2033</v>
       </c>
@@ -2387,7 +2386,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>2034</v>
       </c>
@@ -2395,7 +2394,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>2035</v>
       </c>
@@ -2403,7 +2402,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>2036</v>
       </c>
@@ -2411,7 +2410,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>2037</v>
       </c>
@@ -2419,7 +2418,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>2038</v>
       </c>
@@ -2427,7 +2426,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>2039</v>
       </c>
@@ -2435,7 +2434,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>2040</v>
       </c>
@@ -2443,7 +2442,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>2041</v>
       </c>
@@ -2451,7 +2450,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>2042</v>
       </c>
@@ -2459,7 +2458,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>2043</v>
       </c>
@@ -2467,7 +2466,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>2044</v>
       </c>
@@ -2475,7 +2474,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>2045</v>
       </c>
@@ -2483,7 +2482,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>2046</v>
       </c>
@@ -2491,7 +2490,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>2047</v>
       </c>
@@ -2499,7 +2498,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>2048</v>
       </c>
@@ -2507,7 +2506,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>2049</v>
       </c>
@@ -2515,7 +2514,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>2050</v>
       </c>
@@ -2523,7 +2522,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>2051</v>
       </c>
@@ -2531,7 +2530,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>2052</v>
       </c>
@@ -2539,7 +2538,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>2053</v>
       </c>
@@ -2547,7 +2546,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>2054</v>
       </c>
@@ -2555,7 +2554,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>2055</v>
       </c>
@@ -2563,7 +2562,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>2056</v>
       </c>
@@ -2571,7 +2570,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>2057</v>
       </c>
@@ -2579,7 +2578,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>2058</v>
       </c>
@@ -2587,7 +2586,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>2059</v>
       </c>
@@ -2595,7 +2594,7 @@
         <v>108.7</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>2060</v>
       </c>
@@ -2609,5165 +2608,4563 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB137BA4-4035-472D-AA2B-29C110ABC52B}">
-  <dimension ref="A1:B74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD13CB25-01B4-493C-9025-BBB6EF16C952}">
+  <dimension ref="A1:B570"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.5" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1">
+        <v>44244</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2">
+        <v>44279</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>1988</v>
       </c>
-      <c r="B2">
+      <c r="B9">
         <v>49.6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10">
         <v>1989</v>
       </c>
-      <c r="B3">
+      <c r="B10">
         <v>52.2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11">
         <v>1990</v>
       </c>
-      <c r="B4">
+      <c r="B11">
         <v>55.9</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12">
         <v>1991</v>
       </c>
-      <c r="B5">
+      <c r="B12">
         <v>60.1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13">
         <v>1992</v>
       </c>
-      <c r="B6">
+      <c r="B13">
         <v>62.6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14">
         <v>1993</v>
       </c>
-      <c r="B7">
+      <c r="B14">
         <v>64.2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15">
         <v>1994</v>
       </c>
-      <c r="B8">
+      <c r="B15">
         <v>65.5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16">
         <v>1995</v>
       </c>
-      <c r="B9">
+      <c r="B16">
         <v>67.2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17">
         <v>1996</v>
       </c>
-      <c r="B10">
+      <c r="B17">
         <v>68.8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18">
         <v>1997</v>
       </c>
-      <c r="B11">
+      <c r="B18">
         <v>70.099999999999994</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19">
         <v>1998</v>
       </c>
-      <c r="B12">
+      <c r="B19">
         <v>71.2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20">
         <v>1999</v>
       </c>
-      <c r="B13">
+      <c r="B20">
         <v>72.099999999999994</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21">
         <v>2000</v>
       </c>
-      <c r="B14">
+      <c r="B21">
         <v>72.7</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22">
         <v>2001</v>
       </c>
-      <c r="B15">
+      <c r="B22">
         <v>73.599999999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23">
         <v>2002</v>
       </c>
-      <c r="B16">
+      <c r="B23">
         <v>74.5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24">
         <v>2003</v>
       </c>
-      <c r="B17">
+      <c r="B24">
         <v>75.5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25">
         <v>2004</v>
       </c>
-      <c r="B18">
+      <c r="B25">
         <v>76.5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26">
         <v>2005</v>
       </c>
-      <c r="B19">
+      <c r="B26">
         <v>78.099999999999994</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27">
         <v>2006</v>
       </c>
-      <c r="B20">
+      <c r="B27">
         <v>79.900000000000006</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28">
         <v>2007</v>
       </c>
-      <c r="B21">
+      <c r="B28">
         <v>81.8</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29">
         <v>2008</v>
       </c>
-      <c r="B22">
+      <c r="B29">
         <v>84.7</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30">
         <v>2009</v>
       </c>
-      <c r="B23">
+      <c r="B30">
         <v>86.6</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31">
         <v>2010</v>
       </c>
-      <c r="B24">
+      <c r="B31">
         <v>89.4</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32">
         <v>2011</v>
       </c>
-      <c r="B25">
+      <c r="B32">
         <v>93.4</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33">
         <v>2012</v>
       </c>
-      <c r="B26">
+      <c r="B33">
         <v>96.1</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34">
         <v>2013</v>
       </c>
-      <c r="B27">
+      <c r="B34">
         <v>98.5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35">
         <v>2014</v>
       </c>
-      <c r="B28">
+      <c r="B35">
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36">
         <v>2015</v>
       </c>
-      <c r="B29">
+      <c r="B36">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37">
         <v>2016</v>
       </c>
-      <c r="B30">
+      <c r="B37">
         <v>100.7</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38">
         <v>2017</v>
       </c>
-      <c r="B31">
+      <c r="B38">
         <v>103.4</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39">
         <v>2018</v>
       </c>
-      <c r="B32">
+      <c r="B39">
         <v>105.9</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40">
         <v>2019</v>
       </c>
-      <c r="B33">
+      <c r="B40">
         <v>107.8</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41">
         <v>2020</v>
-      </c>
-      <c r="B34">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>2021</v>
-      </c>
-      <c r="B35">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>2022</v>
-      </c>
-      <c r="B36">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>2023</v>
-      </c>
-      <c r="B37">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>2024</v>
-      </c>
-      <c r="B38">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>2025</v>
-      </c>
-      <c r="B39">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>2026</v>
-      </c>
-      <c r="B40">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>2027</v>
       </c>
       <c r="B41">
         <v>108.7</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>2028</v>
-      </c>
-      <c r="B42">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>2029</v>
-      </c>
-      <c r="B43">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>2030</v>
-      </c>
-      <c r="B44">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>2031</v>
-      </c>
-      <c r="B45">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>2032</v>
-      </c>
-      <c r="B46">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>2033</v>
-      </c>
-      <c r="B47">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>2034</v>
-      </c>
-      <c r="B48">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>2035</v>
-      </c>
-      <c r="B49">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>2036</v>
-      </c>
-      <c r="B50">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>2037</v>
-      </c>
-      <c r="B51">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>2038</v>
-      </c>
-      <c r="B52">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>2039</v>
-      </c>
-      <c r="B53">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>2040</v>
-      </c>
-      <c r="B54">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>2041</v>
-      </c>
-      <c r="B55">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>2042</v>
-      </c>
-      <c r="B56">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>2043</v>
-      </c>
-      <c r="B57">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>2044</v>
-      </c>
-      <c r="B58">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>2045</v>
-      </c>
-      <c r="B59">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>2046</v>
-      </c>
-      <c r="B60">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>2047</v>
-      </c>
-      <c r="B61">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>2048</v>
-      </c>
-      <c r="B62">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>2049</v>
-      </c>
-      <c r="B63">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>2050</v>
-      </c>
-      <c r="B64">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>2051</v>
-      </c>
-      <c r="B65">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>2052</v>
-      </c>
-      <c r="B66">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>2053</v>
-      </c>
-      <c r="B67">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>2054</v>
-      </c>
-      <c r="B68">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>2055</v>
-      </c>
-      <c r="B69">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>2056</v>
-      </c>
-      <c r="B70">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>2057</v>
-      </c>
-      <c r="B71">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>2058</v>
-      </c>
-      <c r="B72">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>2059</v>
-      </c>
-      <c r="B73">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>2060</v>
-      </c>
-      <c r="B74">
-        <v>108.7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD13CB25-01B4-493C-9025-BBB6EF16C952}">
-  <dimension ref="A1:B570"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.5703125" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1">
-        <v>44244</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="2">
-        <v>44279</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>1988</v>
-      </c>
-      <c r="B9">
-        <v>49.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>1989</v>
-      </c>
-      <c r="B10">
-        <v>52.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>1990</v>
-      </c>
-      <c r="B11">
-        <v>55.9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>1991</v>
-      </c>
-      <c r="B12">
-        <v>60.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>1992</v>
-      </c>
-      <c r="B13">
-        <v>62.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>1993</v>
-      </c>
-      <c r="B14">
-        <v>64.2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>1994</v>
-      </c>
-      <c r="B15">
-        <v>65.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>1995</v>
-      </c>
-      <c r="B16">
-        <v>67.2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>1996</v>
-      </c>
-      <c r="B17">
-        <v>68.8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>1997</v>
-      </c>
-      <c r="B18">
-        <v>70.099999999999994</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>1998</v>
-      </c>
-      <c r="B19">
-        <v>71.2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>1999</v>
-      </c>
-      <c r="B20">
-        <v>72.099999999999994</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>2000</v>
-      </c>
-      <c r="B21">
-        <v>72.7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>2001</v>
-      </c>
-      <c r="B22">
-        <v>73.599999999999994</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>2002</v>
-      </c>
-      <c r="B23">
-        <v>74.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>2003</v>
-      </c>
-      <c r="B24">
-        <v>75.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>2004</v>
-      </c>
-      <c r="B25">
-        <v>76.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>2005</v>
-      </c>
-      <c r="B26">
-        <v>78.099999999999994</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>2006</v>
-      </c>
-      <c r="B27">
-        <v>79.900000000000006</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>2007</v>
-      </c>
-      <c r="B28">
-        <v>81.8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>2008</v>
-      </c>
-      <c r="B29">
-        <v>84.7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>2009</v>
-      </c>
-      <c r="B30">
-        <v>86.6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>2010</v>
-      </c>
-      <c r="B31">
-        <v>89.4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>2011</v>
-      </c>
-      <c r="B32">
-        <v>93.4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>2012</v>
-      </c>
-      <c r="B33">
-        <v>96.1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>2013</v>
-      </c>
-      <c r="B34">
-        <v>98.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>2014</v>
-      </c>
-      <c r="B35">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>2015</v>
-      </c>
-      <c r="B36">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>2016</v>
-      </c>
-      <c r="B37">
-        <v>100.7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>2017</v>
-      </c>
-      <c r="B38">
-        <v>103.4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>2018</v>
-      </c>
-      <c r="B39">
-        <v>105.9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>2019</v>
-      </c>
-      <c r="B40">
-        <v>107.8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>2020</v>
-      </c>
-      <c r="B41">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>16</v>
       </c>
       <c r="B42">
         <v>48.6</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B43">
         <v>49.5</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B44">
         <v>49.9</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B45">
         <v>50.5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B46">
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B47">
         <v>52.1</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B48">
         <v>52.5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B49">
         <v>53.3</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B50">
         <v>53.9</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B51">
         <v>55.6</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B52">
         <v>56.4</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B53">
         <v>57.5</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B54">
         <v>57.7</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B55">
         <v>60.3</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B56">
         <v>60.8</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B57">
         <v>61.5</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B58">
         <v>61.7</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B59">
         <v>62.8</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B60">
         <v>62.7</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B61">
         <v>63.1</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B62">
         <v>63.2</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B63">
         <v>64.400000000000006</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B64">
         <v>64.5</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B65">
         <v>64.7</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B66">
         <v>64.7</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B67">
         <v>65.7</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B68">
         <v>65.599999999999994</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B69">
         <v>65.8</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B70">
         <v>66.3</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B71">
         <v>67.3</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B72">
         <v>67.400000000000006</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B73">
         <v>67.7</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B74">
         <v>68.099999999999994</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B75">
         <v>68.900000000000006</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B76">
         <v>68.900000000000006</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B77">
         <v>69.400000000000006</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B78">
         <v>69.400000000000006</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B79">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B80">
         <v>70.3</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B81">
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B82">
         <v>70.5</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B83">
         <v>71.3</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B84">
         <v>71.2</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B85">
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B86">
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B87">
         <v>72.3</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B88">
         <v>72.099999999999994</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B89">
         <v>72.5</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B90">
         <v>72.099999999999994</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B91">
         <v>72.7</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B92">
         <v>72.7</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B93">
         <v>73.2</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B94">
         <v>72.8</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B95">
         <v>73.8</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B96">
         <v>73.8</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B97">
         <v>73.900000000000006</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B98">
         <v>73.900000000000006</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B99">
         <v>74.5</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B100">
         <v>74.599999999999994</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B101">
         <v>75</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B102">
         <v>75</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B103">
         <v>75.5</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B104">
         <v>75.599999999999994</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B105">
         <v>76</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B106">
         <v>75.900000000000006</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B107">
         <v>76.5</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B108">
         <v>76.599999999999994</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B109">
         <v>77.099999999999994</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B110">
         <v>77.3</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B111">
         <v>78</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B112">
         <v>78.400000000000006</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B113">
         <v>78.8</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B114">
         <v>78.7</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B115">
         <v>79.8</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B116">
         <v>80.3</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B117">
         <v>80.900000000000006</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B118">
         <v>81</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B119">
         <v>81.8</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B120">
         <v>81.7</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B121">
         <v>82.6</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B122">
         <v>82.9</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B123">
         <v>84.6</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B124">
         <v>85.7</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B125">
         <v>85.8</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B126">
         <v>85.4</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B127">
         <v>86.4</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B128">
         <v>86.9</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B129">
         <v>87.6</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B130">
         <v>88.2</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B131">
         <v>89.3</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B132">
         <v>89.6</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B133">
         <v>90.5</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B134">
         <v>91.8</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B135">
         <v>93.3</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B136">
         <v>93.8</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B137">
         <v>94.7</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B138">
         <v>95.1</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B139">
         <v>95.8</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B140">
         <v>96.1</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B141">
         <v>97.3</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B142">
         <v>97.7</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B143">
         <v>98.4</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B144">
         <v>98.7</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B145">
         <v>99.3</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B146">
         <v>99.4</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B147">
         <v>100.1</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B148">
         <v>100.1</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B149">
         <v>100.2</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B150">
         <v>99.5</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B151">
         <v>100.1</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B152">
         <v>100.1</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B153">
         <v>100.3</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B154">
         <v>99.8</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B155">
         <v>100.4</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B156">
         <v>100.9</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B157">
         <v>101.5</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B158">
         <v>102</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B159">
         <v>103.2</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B160">
         <v>103.7</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B161">
         <v>104.6</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B162">
         <v>104.7</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B163">
         <v>105.7</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B164">
         <v>106.3</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B165">
         <v>106.9</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B166">
         <v>106.7</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B167">
         <v>107.8</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B168">
         <v>108.3</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B169">
         <v>108.5</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B170">
         <v>108.5</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B171">
         <v>108.5</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B172">
         <v>108.9</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B173">
         <v>109</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B174">
         <v>48.4</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B175">
         <v>48.6</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B176">
         <v>48.7</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B177">
         <v>49.3</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B178">
         <v>49.5</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B179">
         <v>49.7</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B180">
         <v>49.7</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B181">
         <v>49.9</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B182">
         <v>50.1</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B183">
         <v>50.3</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B184">
         <v>50.5</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B185">
         <v>50.6</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B186">
         <v>50.8</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B187">
         <v>51</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B188">
         <v>51.2</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B189">
         <v>51.9</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B190">
         <v>52.2</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B191">
         <v>52.3</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B192">
         <v>52.3</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B193">
         <v>52.4</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B194">
         <v>52.7</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B195">
         <v>53.1</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B196">
         <v>53.3</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B197">
         <v>53.4</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B198">
         <v>53.6</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B199">
         <v>54</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B200">
         <v>54.2</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B201">
         <v>55.2</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B202">
         <v>55.7</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B203">
         <v>55.9</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B204">
         <v>55.8</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B205">
         <v>56.4</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B206">
         <v>57</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B207">
         <v>57.4</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B208">
         <v>57.5</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B209">
         <v>57.5</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B210">
         <v>57.4</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B211">
         <v>57.7</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B212">
         <v>57.9</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B213">
         <v>59.9</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B214">
         <v>60.3</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B215">
         <v>60.6</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B216">
         <v>60.5</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B217">
         <v>60.9</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B218">
         <v>61.1</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B219">
         <v>61.3</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B220">
         <v>61.5</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B221">
         <v>61.6</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B222">
         <v>61.4</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B223">
         <v>61.7</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B224">
         <v>62</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B225">
         <v>62.7</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B226">
         <v>62.9</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B227">
         <v>62.9</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B228">
         <v>62.6</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B229">
         <v>62.7</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B230">
         <v>62.9</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B231">
         <v>63.1</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B232">
         <v>63.1</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B233">
         <v>63.2</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B234">
         <v>62.8</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B235">
         <v>63.2</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B236">
         <v>63.6</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B237">
         <v>64.3</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B238">
         <v>64.5</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B239">
         <v>64.5</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B240">
         <v>64.2</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B241">
         <v>64.5</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B242">
         <v>64.8</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B243">
         <v>64.7</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B244">
         <v>64.599999999999994</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B245">
         <v>64.7</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B246">
         <v>64.5</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B247">
         <v>64.8</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B248">
         <v>65</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B249">
         <v>65.5</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B250">
         <v>65.8</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B251">
         <v>65.8</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B252">
         <v>65.400000000000006</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B253">
         <v>65.7</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B254">
         <v>65.8</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B255">
         <v>65.7</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B256">
         <v>65.7</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B257">
         <v>66</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B258">
         <v>66</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B259">
         <v>66.3</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B260">
         <v>66.7</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B261">
         <v>67</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B262">
         <v>67.400000000000006</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B263">
         <v>67.400000000000006</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B264">
         <v>67.099999999999994</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B265">
         <v>67.400000000000006</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B266">
         <v>67.7</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B267">
         <v>67.599999999999994</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B268">
         <v>67.599999999999994</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B269">
         <v>68</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B270">
         <v>67.8</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B271">
         <v>68.099999999999994</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B272">
         <v>68.400000000000006</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B273">
         <v>68.7</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B274">
         <v>68.900000000000006</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B275">
         <v>69</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B276">
         <v>68.599999999999994</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B277">
         <v>68.900000000000006</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B278">
         <v>69.3</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B279">
         <v>69.3</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B280">
         <v>69.3</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B281">
         <v>69.5</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B282">
         <v>69.2</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B283">
         <v>69.400000000000006</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B284">
         <v>69.5</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B285">
         <v>69.8</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B286">
         <v>70</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B287">
         <v>70.2</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B288">
         <v>69.900000000000006</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B289">
         <v>70.3</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B290">
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B291">
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B292">
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B293">
         <v>70.7</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B294">
         <v>70.3</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B295">
         <v>70.5</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B296">
         <v>70.7</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B297">
         <v>71.099999999999994</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B298">
         <v>71.400000000000006</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B299">
         <v>71.3</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B300">
         <v>71</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B301">
         <v>71.2</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B302">
         <v>71.5</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B303">
         <v>71.5</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B304">
         <v>71.599999999999994</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B305">
         <v>71.8</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B306">
         <v>71.400000000000006</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B307">
         <v>71.5</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B308">
         <v>71.900000000000006</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B309">
         <v>72.2</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B310">
         <v>72.400000000000006</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B311">
         <v>72.3</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B312">
         <v>71.900000000000006</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B313">
         <v>72.099999999999994</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B314">
         <v>72.400000000000006</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B315">
         <v>72.3</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B316">
         <v>72.400000000000006</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B317">
         <v>72.599999999999994</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B318">
         <v>71.900000000000006</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B319">
         <v>72.2</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B320">
         <v>72.3</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B321">
         <v>72.599999999999994</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B322">
         <v>72.8</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B323">
         <v>72.900000000000006</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B324">
         <v>72.5</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B325">
         <v>72.5</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B326">
         <v>73.099999999999994</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B327">
         <v>73.099999999999994</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B328">
         <v>73.2</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B329">
         <v>73.2</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B330">
         <v>72.599999999999994</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B331">
         <v>72.7</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B332">
         <v>73</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B333">
         <v>73.400000000000006</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B334">
         <v>74</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B335">
         <v>74.099999999999994</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B336">
         <v>73.599999999999994</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B337">
         <v>73.900000000000006</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B338">
         <v>74.099999999999994</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B339">
         <v>73.900000000000006</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B340">
         <v>73.8</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B341">
         <v>74</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B342">
         <v>73.7</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B343">
         <v>73.8</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B344">
         <v>74.099999999999994</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B345">
         <v>74.400000000000006</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B346">
         <v>74.599999999999994</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B347">
         <v>74.599999999999994</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B348">
         <v>74.400000000000006</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B349">
         <v>74.599999999999994</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B350">
         <v>74.8</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B351">
         <v>74.900000000000006</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B352">
         <v>74.900000000000006</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B353">
         <v>75.2</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B354">
         <v>74.7</v>
       </c>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B355">
         <v>75</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B356">
         <v>75.3</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B357">
         <v>75.5</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B358">
         <v>75.5</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B359">
         <v>75.400000000000006</v>
       </c>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B360">
         <v>75.3</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B361">
         <v>75.599999999999994</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B362">
         <v>75.900000000000006</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B363">
         <v>76</v>
       </c>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B364">
         <v>75.900000000000006</v>
       </c>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B365">
         <v>76.2</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B366">
         <v>75.8</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B367">
         <v>76</v>
       </c>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B368">
         <v>76.099999999999994</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B369">
         <v>76.400000000000006</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B370">
         <v>76.599999999999994</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B371">
         <v>76.599999999999994</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B372">
         <v>76.400000000000006</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B373">
         <v>76.599999999999994</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B374">
         <v>76.7</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B375">
         <v>76.900000000000006</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B376">
         <v>77</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B377">
         <v>77.400000000000006</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B378">
         <v>77</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B379">
         <v>77.2</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B380">
         <v>77.5</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B381">
         <v>77.8</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B382">
         <v>78.099999999999994</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B383">
         <v>78.099999999999994</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B384">
         <v>78.2</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B385">
         <v>78.400000000000006</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B386">
         <v>78.599999999999994</v>
       </c>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B387">
         <v>78.7</v>
       </c>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B388">
         <v>78.7</v>
       </c>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B389">
         <v>78.900000000000006</v>
       </c>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B390">
         <v>78.5</v>
       </c>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B391">
         <v>78.8</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B392">
         <v>78.900000000000006</v>
       </c>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B393">
         <v>79.400000000000006</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B394">
         <v>79.900000000000006</v>
       </c>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B395">
         <v>80.099999999999994</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B396">
         <v>80</v>
       </c>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B397">
         <v>80.400000000000006</v>
       </c>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B398">
         <v>80.5</v>
       </c>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B399">
         <v>80.599999999999994</v>
       </c>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B400">
         <v>80.8</v>
       </c>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B401">
         <v>81.3</v>
       </c>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B402">
         <v>80.599999999999994</v>
       </c>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B403">
         <v>81</v>
       </c>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B404">
         <v>81.400000000000006</v>
       </c>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B405">
         <v>81.599999999999994</v>
       </c>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B406">
         <v>81.8</v>
       </c>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B407">
         <v>82</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B408">
         <v>81.5</v>
       </c>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B409">
         <v>81.8</v>
       </c>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B410">
         <v>81.900000000000006</v>
       </c>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B411">
         <v>82.3</v>
       </c>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B412">
         <v>82.5</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B413">
         <v>83</v>
       </c>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B414">
         <v>82.4</v>
       </c>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B415">
         <v>83</v>
       </c>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B416">
         <v>83.4</v>
       </c>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B417">
         <v>84</v>
       </c>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B418">
         <v>84.6</v>
       </c>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B419">
         <v>85.2</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B420">
         <v>85.1</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B421">
         <v>85.7</v>
       </c>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B422">
         <v>86.1</v>
       </c>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B423">
         <v>85.9</v>
       </c>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B424">
         <v>85.8</v>
       </c>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B425">
         <v>85.5</v>
       </c>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B426">
         <v>84.9</v>
       </c>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B427">
         <v>85.6</v>
       </c>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B428">
         <v>85.8</v>
       </c>
     </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B429">
         <v>86</v>
       </c>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B430">
         <v>86.4</v>
       </c>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B431">
         <v>86.7</v>
       </c>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B432">
         <v>86.7</v>
       </c>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B433">
         <v>87</v>
       </c>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B434">
         <v>87.1</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B435">
         <v>87.2</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B436">
         <v>87.5</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B437">
         <v>88</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B438">
         <v>87.8</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B439">
         <v>88.2</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B440">
         <v>88.7</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B441">
         <v>89.2</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B442">
         <v>89.4</v>
       </c>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B443">
         <v>89.5</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B444">
         <v>89.3</v>
       </c>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B445">
         <v>89.8</v>
       </c>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B446">
         <v>89.8</v>
       </c>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B447">
         <v>90</v>
       </c>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B448">
         <v>90.3</v>
       </c>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B449">
         <v>91.2</v>
       </c>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B450">
         <v>91.3</v>
       </c>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B451">
         <v>92</v>
       </c>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B452">
         <v>92.2</v>
       </c>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B453">
         <v>93.2</v>
       </c>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B454">
         <v>93.4</v>
       </c>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B455">
         <v>93.3</v>
       </c>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B456">
         <v>93.3</v>
       </c>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B457">
         <v>93.8</v>
       </c>
     </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B458">
         <v>94.4</v>
       </c>
     </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B459">
         <v>94.5</v>
       </c>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B460">
         <v>94.6</v>
       </c>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B461">
         <v>95.1</v>
       </c>
     </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B462">
         <v>94.6</v>
       </c>
     </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B463">
         <v>95.1</v>
       </c>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B464">
         <v>95.4</v>
       </c>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B465">
         <v>96</v>
       </c>
     </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B466">
         <v>95.9</v>
       </c>
     </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B467">
         <v>95.5</v>
       </c>
     </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B468">
         <v>95.6</v>
       </c>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B469">
         <v>96.1</v>
       </c>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B470">
         <v>96.5</v>
       </c>
     </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B471">
         <v>97</v>
       </c>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B472">
         <v>97.2</v>
       </c>
     </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B473">
         <v>97.6</v>
       </c>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B474">
         <v>97.1</v>
       </c>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B475">
         <v>97.8</v>
       </c>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B476">
         <v>98.1</v>
       </c>
     </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B477">
         <v>98.3</v>
       </c>
     </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B478">
         <v>98.5</v>
       </c>
     </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B479">
         <v>98.3</v>
       </c>
     </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B480">
         <v>98.3</v>
       </c>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B481">
         <v>98.7</v>
       </c>
     </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B482">
         <v>99.1</v>
       </c>
     </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B483">
         <v>99.1</v>
       </c>
     </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B484">
         <v>99.2</v>
       </c>
     </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B485">
         <v>99.6</v>
       </c>
     </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B486">
         <v>99</v>
       </c>
     </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B487">
         <v>99.5</v>
       </c>
     </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B488">
         <v>99.7</v>
       </c>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B489">
         <v>100.1</v>
       </c>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B490">
         <v>100</v>
       </c>
     </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B491">
         <v>100.2</v>
       </c>
     </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B492">
         <v>99.9</v>
       </c>
     </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B493">
         <v>100.2</v>
       </c>
     </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B494">
         <v>100.3</v>
       </c>
     </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B495">
         <v>100.4</v>
       </c>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B496">
         <v>100.1</v>
       </c>
     </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B497">
         <v>100.1</v>
       </c>
     </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B498">
         <v>99.3</v>
       </c>
     </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B499">
         <v>99.5</v>
       </c>
     </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B500">
         <v>99.7</v>
       </c>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B501">
         <v>99.9</v>
       </c>
     </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B502">
         <v>100.1</v>
       </c>
     </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B503">
         <v>100.2</v>
       </c>
     </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B504">
         <v>100</v>
       </c>
     </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B505">
         <v>100.3</v>
       </c>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B506">
         <v>100.2</v>
       </c>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B507">
         <v>100.3</v>
       </c>
     </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B508">
         <v>100.3</v>
       </c>
     </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B509">
         <v>100.3</v>
       </c>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B510">
         <v>99.5</v>
       </c>
     </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B511">
         <v>99.8</v>
       </c>
     </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B512">
         <v>100.2</v>
       </c>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B513">
         <v>100.2</v>
       </c>
     </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B514">
         <v>100.4</v>
       </c>
     </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B515">
         <v>100.6</v>
       </c>
     </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B516">
         <v>100.6</v>
       </c>
     </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B517">
         <v>100.9</v>
       </c>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B518">
         <v>101.1</v>
       </c>
     </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B519">
         <v>101.2</v>
       </c>
     </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B520">
         <v>101.4</v>
       </c>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B521">
         <v>101.9</v>
       </c>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B522">
         <v>101.4</v>
       </c>
     </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B523">
         <v>102.1</v>
       </c>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B524">
         <v>102.5</v>
       </c>
     </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B525">
         <v>102.9</v>
       </c>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B526">
         <v>103.3</v>
       </c>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B527">
         <v>103.3</v>
       </c>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B528">
         <v>103.2</v>
       </c>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B529">
         <v>103.8</v>
       </c>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B530">
         <v>104.1</v>
       </c>
     </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B531">
         <v>104.2</v>
       </c>
     </row>
-    <row r="532" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B532">
         <v>104.6</v>
       </c>
     </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B533">
         <v>104.9</v>
       </c>
     </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B534">
         <v>104.4</v>
       </c>
     </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B535">
         <v>104.9</v>
       </c>
     </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B536">
         <v>105</v>
       </c>
     </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B537">
         <v>105.4</v>
       </c>
     </row>
-    <row r="538" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B538">
         <v>105.8</v>
       </c>
     </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B539">
         <v>105.8</v>
       </c>
     </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B540">
         <v>105.8</v>
       </c>
     </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B541">
         <v>106.5</v>
       </c>
     </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B542">
         <v>106.6</v>
       </c>
     </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B543">
         <v>106.7</v>
       </c>
     </row>
-    <row r="544" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B544">
         <v>107</v>
       </c>
     </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B545">
         <v>107.1</v>
       </c>
     </row>
-    <row r="546" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B546">
         <v>106.3</v>
       </c>
     </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B547">
         <v>106.8</v>
       </c>
     </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B548">
         <v>107</v>
       </c>
     </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B549">
         <v>107.6</v>
       </c>
     </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B550">
         <v>107.9</v>
       </c>
     </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B551">
         <v>107.9</v>
       </c>
     </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B552">
         <v>107.9</v>
       </c>
     </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B553">
         <v>108.4</v>
       </c>
     </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B554">
         <v>108.5</v>
       </c>
     </row>
-    <row r="555" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B555">
         <v>108.3</v>
       </c>
     </row>
-    <row r="556" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B556">
         <v>108.5</v>
       </c>
     </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B557">
         <v>108.5</v>
       </c>
     </row>
-    <row r="558" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B558">
         <v>108.2</v>
       </c>
     </row>
-    <row r="559" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B559">
         <v>108.6</v>
       </c>
     </row>
-    <row r="560" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B560">
         <v>108.6</v>
       </c>
     </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B561">
         <v>108.5</v>
       </c>
     </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B562">
         <v>108.5</v>
       </c>
     </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B563">
         <v>108.6</v>
       </c>
     </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B564">
         <v>109.1</v>
       </c>
     </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B565">
         <v>108.6</v>
       </c>
     </row>
-    <row r="566" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B566">
         <v>109.1</v>
       </c>
     </row>
-    <row r="567" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B567">
         <v>109.1</v>
       </c>
     </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B568">
         <v>108.9</v>
       </c>
     </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B569">
         <v>109.2</v>
       </c>
     </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B570">
         <v>109</v>
